--- a/model_fitting/2010/results_chisquare.xlsx
+++ b/model_fitting/2010/results_chisquare.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80786.84</v>
+        <v>80787.71000000001</v>
       </c>
       <c r="C2" t="n">
         <v>32</v>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>595.74</v>
+        <v>595.76</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10906.03</v>
+        <v>10906.05</v>
       </c>
       <c r="C4" t="n">
         <v>88</v>
@@ -519,7 +519,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8777</v>
+        <v>0.8776</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>988.5</v>
+        <v>988.49</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
